--- a/04-pinecastle-software-grc-program/04-control-framework-crosswalk/artifacts/Pinecastle-Control-Framework-Crosswalk-and-Testing.xlsx
+++ b/04-pinecastle-software-grc-program/04-control-framework-crosswalk/artifacts/Pinecastle-Control-Framework-Crosswalk-and-Testing.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard'!$A$1:$H$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Control Library'!$A$1:$L$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Framework Crosswalk'!$A$1:$H$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Test Workpapers'!$A$1:$J$6</definedName>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B8" s="34" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D8" s="31" t="inlineStr">
         <is>
